--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487411_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487411_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8319</v>
+        <v>1.6983</v>
       </c>
       <c r="E2" t="n">
         <v>5.9117</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.0798</v>
+        <v>-4.2134</v>
       </c>
       <c r="G2" t="n">
         <v>3.8177</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4808</v>
+        <v>0.3471</v>
       </c>
       <c r="T2" t="n">
         <v>0.4382</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0426</v>
+        <v>-0.091</v>
       </c>
       <c r="V2" t="n">
         <v>0.2754</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6415</v>
+        <v>0.8761</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6116</v>
+        <v>0.7169</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9701</v>
+        <v>0.1593</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0935</v>
+        <v>0.3386</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1293</v>
+        <v>-1.3484</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2228</v>
+        <v>1.6871</v>
       </c>
       <c r="J3" t="n">
-        <v>1.106</v>
+        <v>2.3562</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2977</v>
+        <v>0.2806</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8083</v>
+        <v>2.0756</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0124</v>
+        <v>-2.0176</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.427</v>
+        <v>-1.629</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4145</v>
+        <v>-0.3886</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1751</v>
+        <v>-2.9377</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9585</v>
+        <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9812</v>
+        <v>-0.0121</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6807</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6995</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2166</v>
+        <v>0.9412</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>N. BARREIRO BUCETA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8226</v>
+        <v>0.4473</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7169</v>
+        <v>3.0044</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1058</v>
+        <v>-2.5572</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3386</v>
+        <v>2.8124</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3484</v>
+        <v>-0.2031</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6871</v>
+        <v>3.0156</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3562</v>
+        <v>4.152</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2806</v>
+        <v>0.3385</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0756</v>
+        <v>3.8135</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0176</v>
+        <v>-1.3395</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.629</v>
+        <v>-0.5416</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3886</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>2.546</v>
+        <v>1.7626</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0655</v>
+        <v>0.5012</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.4976</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1473</v>
+        <v>0.0037</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9412</v>
+        <v>-3.6498</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2166</v>
+        <v>-0.6659</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2754</v>
+        <v>-2.9839</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. BARREIRO BUCETA</t>
+          <t>C. VALDES ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.474</v>
+        <v>0.4452</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0044</v>
+        <v>0.8579</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5304</v>
+        <v>-0.4127</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8124</v>
+        <v>-0.2909</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2031</v>
+        <v>-0.0892</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0156</v>
+        <v>-0.2017</v>
       </c>
       <c r="J5" t="n">
-        <v>4.152</v>
+        <v>1.5924</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3385</v>
+        <v>1.2691</v>
       </c>
       <c r="L5" t="n">
-        <v>3.8135</v>
+        <v>0.3233</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3395</v>
+        <v>-1.8833</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5416</v>
+        <v>-1.3582</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.525</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7626</v>
+        <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>0.528</v>
+        <v>-0.6349</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4976</v>
+        <v>-0.0306</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0304</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.6498</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.9839</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. VALDES ALVAREZ</t>
+          <t>J. FERNANDEZ PILLADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0893</v>
+        <v>0.2102</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4486</v>
+        <v>0.1175</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3593</v>
+        <v>0.0927</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2909</v>
+        <v>-1.5404</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0892</v>
+        <v>-2.424</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2017</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5924</v>
+        <v>-0.1249</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2691</v>
+        <v>-0.5887</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3233</v>
+        <v>0.4638</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8833</v>
+        <v>-1.4156</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3582</v>
+        <v>-1.8353</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.525</v>
+        <v>0.4197</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3709</v>
+        <v>1.9585</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3502</v>
+        <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9908</v>
+        <v>-0.2079</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4399</v>
+        <v>0.4382</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5508</v>
+        <v>-0.6461</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ PILLADO</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3595</v>
+        <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2919</v>
+        <v>1.0766</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0677</v>
+        <v>-0.9166</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5404</v>
+        <v>0.0935</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.424</v>
+        <v>-1.1293</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8836000000000001</v>
+        <v>1.2228</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1249</v>
+        <v>1.106</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5887</v>
+        <v>0.2977</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4638</v>
+        <v>0.8083</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4156</v>
+        <v>-1.0124</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8353</v>
+        <v>-1.427</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4197</v>
+        <v>0.4145</v>
       </c>
       <c r="P7" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.1751</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.9585</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.1958</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.1543</v>
-      </c>
       <c r="S7" t="n">
-        <v>-0.7776</v>
+        <v>0.4996</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0288</v>
+        <v>1.1457</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8064</v>
+        <v>-0.6461</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5143</v>
+        <v>-0.4433</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.3129</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0032</v>
+        <v>-0.1304</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6078</v>
@@ -1078,13 +1078,13 @@
         <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3973</v>
+        <v>-0.3263</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3564</v>
+        <v>-0.1517</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0409</v>
+        <v>-0.1745</v>
       </c>
       <c r="V8" t="n">
         <v>1.8825</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. LOPE REBOLLO</t>
+          <t>L. GARCÍA SINDIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0032</v>
+        <v>-0.6178</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2769</v>
+        <v>-0.1511</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.4667</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.286</v>
+        <v>-2.5712</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6802</v>
+        <v>-1.5097</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3941</v>
+        <v>-1.0615</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1212</v>
+        <v>-1.3536</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.1225</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1212</v>
+        <v>-1.4761</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4073</v>
+        <v>-1.2176</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6802</v>
+        <v>-1.6322</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2729</v>
+        <v>0.4145</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2252</v>
+        <v>-0.7493</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.1817</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3559</v>
+        <v>-0.931</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5507</v>
+        <v>1.3318</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5507</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. GARCÍA SINDIN</t>
+          <t>S. LOPE REBOLLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0317</v>
+        <v>-1.23</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4581</v>
+        <v>-0.5839</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5736</v>
+        <v>-0.6461</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5712</v>
+        <v>-0.286</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5097</v>
+        <v>-0.6802</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0615</v>
+        <v>0.3941</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3536</v>
+        <v>0.1212</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1225</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4761</v>
+        <v>0.1212</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2176</v>
+        <v>-0.4073</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6322</v>
+        <v>-0.6802</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4145</v>
+        <v>0.2729</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3709</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1632</v>
+        <v>-0.0016</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1253</v>
+        <v>0.2741</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0379</v>
+        <v>-0.2757</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3318</v>
+        <v>-0.5507</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1152</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6665</v>
+        <v>-1.4885</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7914</v>
+        <v>-0.5868</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.875</v>
+        <v>-0.9018</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3974</v>
@@ -1312,13 +1312,13 @@
         <v>0.9792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7771</v>
+        <v>-0.5992</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0065</v>
+        <v>0.1982</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7706</v>
+        <v>-0.7974</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2754</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3258</v>
+        <v>-4.099</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6467</v>
+        <v>-3.3397</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6792</v>
+        <v>-0.7593</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8887</v>
@@ -1390,13 +1390,13 @@
         <v>0.9792</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6169</v>
+        <v>-0.3901</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2311</v>
+        <v>0.5381</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.848</v>
+        <v>-0.9282</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6659</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.041700000000001</v>
+        <v>-4.0415</v>
       </c>
       <c r="E13" t="n">
         <v>6.710599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.7524</v>
+        <v>-10.7522</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5202</v>
+        <v>-1.520200000000001</v>
       </c>
       <c r="H13" t="n">
         <v>-12.2544</v>
@@ -1444,7 +1444,7 @@
         <v>12.6197</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6509999999999999</v>
+        <v>0.651</v>
       </c>
       <c r="L13" t="n">
         <v>11.9687</v>
@@ -1456,7 +1456,7 @@
         <v>-12.9053</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2349</v>
+        <v>-1.234900000000001</v>
       </c>
       <c r="P13" t="n">
         <v>0.9791999999999996</v>
@@ -1468,13 +1468,13 @@
         <v>17.6261</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5732</v>
+        <v>-1.5735</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6111</v>
+        <v>3.6112</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.184299999999999</v>
+        <v>-5.184400000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-1.9275</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8582</v>
+        <v>4.6204</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9347</v>
+        <v>3.5254</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9235</v>
+        <v>1.0951</v>
       </c>
       <c r="G14" t="n">
         <v>5.7442</v>
@@ -1546,13 +1546,13 @@
         <v>2.546</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9884</v>
+        <v>1.7506</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5474</v>
+        <v>1.138</v>
       </c>
       <c r="U14" t="n">
-        <v>0.441</v>
+        <v>0.6125</v>
       </c>
       <c r="V14" t="n">
         <v>1.4344</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9061</v>
+        <v>3.2534</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0725</v>
+        <v>3.0239</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1665</v>
+        <v>0.2294</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.286</v>
+        <v>0.2377</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7306</v>
+        <v>1.228</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5554</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2245</v>
+        <v>2.3012</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1889</v>
+        <v>1.1551</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0356</v>
+        <v>1.1461</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0615</v>
+        <v>-2.0635</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5416</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5198</v>
+        <v>-2.1364</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1543</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1958</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3502</v>
+        <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0953</v>
+        <v>0.9166</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7256</v>
+        <v>0.8563</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3697</v>
+        <v>0.0603</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0576</v>
+        <v>2.4908</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7673</v>
+        <v>1.8249</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8249</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2356</v>
+        <v>2.459</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8193</v>
+        <v>2.5608</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5837</v>
+        <v>-0.1018</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2377</v>
+        <v>-1.286</v>
       </c>
       <c r="H16" t="n">
-        <v>1.228</v>
+        <v>-0.7306</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-0.5554</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3012</v>
+        <v>-0.2245</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1551</v>
+        <v>-0.1889</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1461</v>
+        <v>-0.0356</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0635</v>
+        <v>-1.0615</v>
       </c>
       <c r="N16" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.5416</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.1364</v>
+        <v>-0.5198</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3917</v>
+        <v>2.1543</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>-0.1958</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5668</v>
+        <v>2.3502</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1012</v>
+        <v>1.6482</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6516</v>
+        <v>1.2139</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7528</v>
+        <v>0.4343</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4908</v>
+        <v>-0.0576</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8249</v>
+        <v>1.7673</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6659</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0186</v>
+        <v>1.4666</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5059</v>
+        <v>-0.3012</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5245</v>
+        <v>1.7678</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0496</v>
@@ -1780,13 +1780,13 @@
         <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1069</v>
+        <v>0.3411</v>
       </c>
       <c r="T17" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.2994</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2016</v>
+        <v>0.0418</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9616</v>
+        <v>1.3192</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3997</v>
+        <v>1.8403</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5620000000000001</v>
+        <v>-0.5211</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5343</v>
+        <v>0.392</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2818</v>
+        <v>0.1644</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7475000000000001</v>
+        <v>0.2277</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4624</v>
+        <v>2.0691</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7349</v>
+        <v>0.7758</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7275</v>
+        <v>1.2933</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9281</v>
+        <v>-1.677</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5468</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.475</v>
+        <v>-1.0656</v>
       </c>
       <c r="P18" t="n">
         <v>0.5875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1602</v>
+        <v>-0.3263</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0835</v>
+        <v>-0.0329</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0767</v>
+        <v>-0.2933</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8683999999999999</v>
+        <v>1.1174</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6356</v>
+        <v>0.502</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7672</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.392</v>
+        <v>0.5343</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1644</v>
+        <v>1.2818</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2277</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0691</v>
+        <v>1.4624</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7758</v>
+        <v>0.7349</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2933</v>
+        <v>0.7275</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.677</v>
+        <v>-0.9281</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.5468</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0656</v>
+        <v>-1.475</v>
       </c>
       <c r="P19" t="n">
         <v>0.5875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7771</v>
+        <v>-0.0044</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2376</v>
+        <v>0.0188</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5395</v>
+        <v>-0.0232</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>R. REY ARTIGAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2645</v>
+        <v>1.0741</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1195</v>
+        <v>1.3876</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.855</v>
+        <v>-0.3135</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8378</v>
+        <v>1.1146</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0058</v>
+        <v>1.8213</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8435</v>
+        <v>-0.7067</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0956</v>
+        <v>2.2396</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9339</v>
+        <v>2.1588</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1617</v>
+        <v>0.0808</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9333</v>
+        <v>-1.125</v>
       </c>
       <c r="N20" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.3375</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.0052</v>
+        <v>-0.7875</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3709</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9377</v>
+        <v>-1.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9225</v>
+        <v>-0.3158</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1943</v>
+        <v>-0.2276</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2718</v>
+        <v>-0.0882</v>
       </c>
       <c r="V20" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="W20" t="n">
         <v>0.5507</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.7673</v>
-      </c>
       <c r="X20" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. REY ARTIGAS</t>
+          <t>L. SANCHEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2213</v>
+        <v>-0.0698</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0806</v>
+        <v>0.1136</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8593</v>
+        <v>-0.1835</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1146</v>
+        <v>-0.3102</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8213</v>
+        <v>-0.0881</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7067</v>
+        <v>-0.2221</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2396</v>
+        <v>0.4283</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1588</v>
+        <v>0.3879</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0808</v>
+        <v>0.0404</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.125</v>
+        <v>-0.7385</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3375</v>
+        <v>-0.476</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7875</v>
+        <v>-0.2625</v>
       </c>
       <c r="P21" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.1958</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.3471</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.1188</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.2283</v>
+      </c>
+      <c r="V21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.1751</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.1751</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-1.1686</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.5346</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.634</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.2754</v>
-      </c>
       <c r="W21" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. SANCHEZ VAZQUEZ</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3694</v>
+        <v>-0.1153</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1136</v>
+        <v>1.3008</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4831</v>
+        <v>-1.4161</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3102</v>
+        <v>-0.8378</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0881</v>
+        <v>1.0058</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2221</v>
+        <v>-1.8435</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4283</v>
+        <v>1.0956</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3879</v>
+        <v>0.9339</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0404</v>
+        <v>0.1617</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7385</v>
+        <v>-1.9333</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.476</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2625</v>
+        <v>-2.0052</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5875</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1958</v>
+        <v>-2.9377</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6468</v>
+        <v>1.5427</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1188</v>
+        <v>1.3756</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.528</v>
+        <v>0.167</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.7673</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8605</v>
+        <v>-1.3055</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6627</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1978</v>
+        <v>-0.4381</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8437</v>
@@ -2248,13 +2248,13 @@
         <v>1.7626</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2138</v>
+        <v>0.3411</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5987</v>
+        <v>0.394</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8126</v>
+        <v>-0.0529</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3905</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.0627</v>
+        <v>-5.6844</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2546</v>
+        <v>-2.3336</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8081</v>
+        <v>-3.3509</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1754</v>
@@ -2326,13 +2326,13 @@
         <v>1.3709</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2583</v>
+        <v>0.12</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6534</v>
+        <v>0.2676</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6048</v>
+        <v>-0.1476</v>
       </c>
       <c r="V24" t="n">
         <v>-3.0415</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.041699999999998</v>
+        <v>8.135100000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>10.7523</v>
+        <v>10.7522</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.710699999999999</v>
+        <v>-2.6173</v>
       </c>
       <c r="G25" t="n">
-        <v>1.5201</v>
+        <v>1.520100000000001</v>
       </c>
       <c r="H25" t="n">
         <v>12.2542</v>
@@ -2395,7 +2395,7 @@
         <v>-11.9686</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9793999999999997</v>
+        <v>-0.9793999999999998</v>
       </c>
       <c r="Q25" t="n">
         <v>-17.6262</v>
@@ -2404,13 +2404,13 @@
         <v>16.6471</v>
       </c>
       <c r="S25" t="n">
-        <v>1.573300000000001</v>
+        <v>5.6667</v>
       </c>
       <c r="T25" t="n">
-        <v>5.1844</v>
+        <v>5.1843</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.6111</v>
+        <v>0.4824000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>1.9276</v>
